--- a/luban-excels/bak2/xlsx/Main.xlsx
+++ b/luban-excels/bak2/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="865">
   <si>
     <t>Dog</t>
   </si>
@@ -552,6 +552,24 @@
   </si>
   <si>
     <t>秒，新手阶段结束后与第一个正式盲盒的间隔时间</t>
+  </si>
+  <si>
+    <t>LinkTreeVisibleBannerCount</t>
+  </si>
+  <si>
+    <t>LinkTree最佳显示条目数量</t>
+  </si>
+  <si>
+    <t>未领取奖励的条目和固定条目数量之和不足该值只，以已领取奖励的条目填充占位</t>
+  </si>
+  <si>
+    <t>SteamPlaytimeDropLeadSeconds</t>
+  </si>
+  <si>
+    <t>Steam提前准备盲盒的秒数</t>
+  </si>
+  <si>
+    <t>掉落提前秒数Steam游玩时间掉落相对本地盲盒展示时间提前请求的秒数，用于避开服务器计时边界。正式配置时改为60</t>
   </si>
   <si>
     <t>IconName</t>
@@ -4188,28 +4206,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C1" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="D1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="E1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="F1" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="G1" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="H1" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="I1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4226,16 +4244,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="F2" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4246,28 +4264,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4275,1333 +4293,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C4" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="D4" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E4" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="F4" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="G4" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="H4" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="I4" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D5" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="E5" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="F5" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G5" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="D6" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="E6" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F6" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G6" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D7" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="E7" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="F7" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G7" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D8" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="E8" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="F8" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G8" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="D9" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="E9" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F9" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G9" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="D10" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="E10" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="F10" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G10" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="D11" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="E11" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F11" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G11" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="D12" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="E12" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F12" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G12" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="D13" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="E13" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F13" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G13" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D14" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E14" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="F14" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G14" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="D15" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="E15" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="F15" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G15" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="D16" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="E16" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F16" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G16" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="D17" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="E17" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F17" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G17" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="D18" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="E18" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F18" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G18" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D19" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="E19" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F19" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G19" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D20" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="E20" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F20" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G20" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="D21" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="E21" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F21" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G21" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D22" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="E22" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F22" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G22" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D23" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="E23" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F23" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G23" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="D24" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="E24" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F24" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G24" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D25" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="E25" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F25" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G25" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="D26" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="E26" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F26" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G26" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="D27" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="E27" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="F27" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G27" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="D28" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="E28" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F28" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G28" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="D29" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="E29" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F29" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G29" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="D30" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="E30" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F30" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G30" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="D31" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="E31" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F31" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G31" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="D32" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="E32" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F32" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G32" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="D33" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="E33" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F33" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G33" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="D34" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="E34" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F34" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G34" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="D35" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="E35" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F35" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G35" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="D36" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="E36" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F36" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G36" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="D37" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="E37" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F37" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G37" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="D38" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="E38" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F38" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G38" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="D39" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="E39" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F39" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G39" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="D40" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="E40" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F40" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G40" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="D41" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="E41" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F41" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G41" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="D42" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="E42" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F42" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G42" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="D43" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="E43" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F43" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G43" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="D44" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="E44" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F44" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G44" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="D45" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="E45" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F45" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G45" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="D46" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="E46" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F46" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G46" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D47" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="E47" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F47" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G47" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="D48" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="E48" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F48" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G48" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="D49" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="E49" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F49" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G49" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5609,25 +5627,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="D50" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="E50" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="F50" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="G50" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5635,25 +5653,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="D51" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="E51" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="F51" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="G51" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -6051,7 +6069,7 @@
         <v>158</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>159</v>
@@ -6126,16 +6144,38 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="2">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="2">
+        <v>60</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2"/>
@@ -6183,55 +6223,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="L1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="M1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="N1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="P1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="Q1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="R1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="S1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="T1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6302,10 +6342,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6319,55 +6359,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E4" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H4" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="I4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="L4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="M4" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="N4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="O4" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="P4" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="Q4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="R4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="S4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="T4" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6375,58 +6415,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E5" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="I5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="J5" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="K5" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="L5" t="s">
+        <v>221</v>
+      </c>
+      <c r="M5" t="s">
         <v>215</v>
       </c>
-      <c r="M5" t="s">
-        <v>209</v>
-      </c>
       <c r="N5" t="s">
+        <v>222</v>
+      </c>
+      <c r="O5" t="s">
+        <v>223</v>
+      </c>
+      <c r="P5" t="s">
         <v>216</v>
       </c>
-      <c r="O5" t="s">
-        <v>217</v>
-      </c>
-      <c r="P5" t="s">
-        <v>210</v>
-      </c>
       <c r="Q5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="R5" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="S5" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="T5" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -6434,58 +6474,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" t="s">
+        <v>224</v>
+      </c>
+      <c r="G6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I6" t="s">
+        <v>218</v>
+      </c>
+      <c r="J6" t="s">
+        <v>219</v>
+      </c>
+      <c r="K6" t="s">
+        <v>220</v>
+      </c>
+      <c r="L6" t="s">
+        <v>221</v>
+      </c>
+      <c r="M6" t="s">
+        <v>215</v>
+      </c>
+      <c r="N6" t="s">
         <v>222</v>
       </c>
-      <c r="D6" t="s">
+      <c r="O6" t="s">
         <v>223</v>
       </c>
-      <c r="E6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F6" t="s">
-        <v>218</v>
-      </c>
-      <c r="G6" t="s">
-        <v>180</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="P6" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q6" t="s">
         <v>224</v>
       </c>
-      <c r="I6" t="s">
-        <v>212</v>
-      </c>
-      <c r="J6" t="s">
-        <v>213</v>
-      </c>
-      <c r="K6" t="s">
-        <v>214</v>
-      </c>
-      <c r="L6" t="s">
-        <v>215</v>
-      </c>
-      <c r="M6" t="s">
-        <v>209</v>
-      </c>
-      <c r="N6" t="s">
-        <v>216</v>
-      </c>
-      <c r="O6" t="s">
-        <v>217</v>
-      </c>
-      <c r="P6" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>218</v>
-      </c>
       <c r="R6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="S6" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="T6" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6493,58 +6533,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" t="s">
+        <v>215</v>
+      </c>
+      <c r="F7" t="s">
         <v>225</v>
       </c>
-      <c r="D7" t="s">
+      <c r="G7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" t="s">
+        <v>233</v>
+      </c>
+      <c r="I7" t="s">
+        <v>218</v>
+      </c>
+      <c r="J7" t="s">
+        <v>219</v>
+      </c>
+      <c r="K7" t="s">
+        <v>220</v>
+      </c>
+      <c r="L7" t="s">
+        <v>221</v>
+      </c>
+      <c r="M7" t="s">
+        <v>215</v>
+      </c>
+      <c r="N7" t="s">
+        <v>222</v>
+      </c>
+      <c r="O7" t="s">
+        <v>223</v>
+      </c>
+      <c r="P7" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>224</v>
+      </c>
+      <c r="R7" t="s">
+        <v>225</v>
+      </c>
+      <c r="S7" t="s">
         <v>226</v>
       </c>
-      <c r="E7" t="s">
-        <v>209</v>
-      </c>
-      <c r="F7" t="s">
-        <v>219</v>
-      </c>
-      <c r="G7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="T7" t="s">
         <v>227</v>
-      </c>
-      <c r="I7" t="s">
-        <v>212</v>
-      </c>
-      <c r="J7" t="s">
-        <v>213</v>
-      </c>
-      <c r="K7" t="s">
-        <v>214</v>
-      </c>
-      <c r="L7" t="s">
-        <v>215</v>
-      </c>
-      <c r="M7" t="s">
-        <v>209</v>
-      </c>
-      <c r="N7" t="s">
-        <v>216</v>
-      </c>
-      <c r="O7" t="s">
-        <v>217</v>
-      </c>
-      <c r="P7" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>218</v>
-      </c>
-      <c r="R7" t="s">
-        <v>219</v>
-      </c>
-      <c r="S7" t="s">
-        <v>220</v>
-      </c>
-      <c r="T7" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -6552,58 +6592,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D8" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8" t="s">
+        <v>223</v>
+      </c>
+      <c r="G8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H8" t="s">
+        <v>236</v>
+      </c>
+      <c r="I8" t="s">
+        <v>218</v>
+      </c>
+      <c r="J8" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" t="s">
+        <v>220</v>
+      </c>
+      <c r="L8" t="s">
+        <v>221</v>
+      </c>
+      <c r="M8" t="s">
+        <v>215</v>
+      </c>
+      <c r="N8" t="s">
+        <v>222</v>
+      </c>
+      <c r="O8" t="s">
+        <v>223</v>
+      </c>
+      <c r="P8" t="s">
         <v>216</v>
       </c>
-      <c r="F8" t="s">
-        <v>217</v>
-      </c>
-      <c r="G8" t="s">
-        <v>180</v>
-      </c>
-      <c r="H8" t="s">
-        <v>230</v>
-      </c>
-      <c r="I8" t="s">
-        <v>212</v>
-      </c>
-      <c r="J8" t="s">
-        <v>213</v>
-      </c>
-      <c r="K8" t="s">
-        <v>214</v>
-      </c>
-      <c r="L8" t="s">
-        <v>215</v>
-      </c>
-      <c r="M8" t="s">
-        <v>209</v>
-      </c>
-      <c r="N8" t="s">
-        <v>216</v>
-      </c>
-      <c r="O8" t="s">
-        <v>217</v>
-      </c>
-      <c r="P8" t="s">
-        <v>210</v>
-      </c>
       <c r="Q8" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="R8" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="S8" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="T8" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6611,58 +6651,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D9" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E9" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F9" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I9" t="s">
+        <v>239</v>
+      </c>
+      <c r="J9" t="s">
         <v>219</v>
       </c>
-      <c r="G9" t="s">
-        <v>180</v>
-      </c>
-      <c r="H9" t="s">
-        <v>211</v>
-      </c>
-      <c r="I9" t="s">
-        <v>233</v>
-      </c>
-      <c r="J9" t="s">
-        <v>213</v>
-      </c>
       <c r="K9" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="L9" t="s">
+        <v>221</v>
+      </c>
+      <c r="M9" t="s">
         <v>215</v>
       </c>
-      <c r="M9" t="s">
-        <v>209</v>
-      </c>
       <c r="N9" t="s">
+        <v>222</v>
+      </c>
+      <c r="O9" t="s">
+        <v>223</v>
+      </c>
+      <c r="P9" t="s">
         <v>216</v>
       </c>
-      <c r="O9" t="s">
-        <v>217</v>
-      </c>
-      <c r="P9" t="s">
-        <v>210</v>
-      </c>
       <c r="Q9" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="R9" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="S9" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="T9" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6670,58 +6710,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D10" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" t="s">
         <v>216</v>
       </c>
-      <c r="F10" t="s">
-        <v>210</v>
-      </c>
       <c r="G10" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="I10" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="J10" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="K10" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="L10" t="s">
+        <v>221</v>
+      </c>
+      <c r="M10" t="s">
         <v>215</v>
       </c>
-      <c r="M10" t="s">
-        <v>209</v>
-      </c>
       <c r="N10" t="s">
+        <v>222</v>
+      </c>
+      <c r="O10" t="s">
+        <v>223</v>
+      </c>
+      <c r="P10" t="s">
         <v>216</v>
       </c>
-      <c r="O10" t="s">
-        <v>217</v>
-      </c>
-      <c r="P10" t="s">
-        <v>210</v>
-      </c>
       <c r="Q10" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="R10" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="S10" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="T10" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6729,58 +6769,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D11" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E11" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F11" t="s">
+        <v>227</v>
+      </c>
+      <c r="G11" t="s">
+        <v>186</v>
+      </c>
+      <c r="H11" t="s">
+        <v>230</v>
+      </c>
+      <c r="I11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J11" t="s">
+        <v>219</v>
+      </c>
+      <c r="K11" t="s">
+        <v>220</v>
+      </c>
+      <c r="L11" t="s">
         <v>221</v>
       </c>
-      <c r="G11" t="s">
-        <v>180</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="M11" t="s">
+        <v>215</v>
+      </c>
+      <c r="N11" t="s">
+        <v>222</v>
+      </c>
+      <c r="O11" t="s">
+        <v>223</v>
+      </c>
+      <c r="P11" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q11" t="s">
         <v>224</v>
       </c>
-      <c r="I11" t="s">
-        <v>233</v>
-      </c>
-      <c r="J11" t="s">
-        <v>213</v>
-      </c>
-      <c r="K11" t="s">
-        <v>214</v>
-      </c>
-      <c r="L11" t="s">
-        <v>215</v>
-      </c>
-      <c r="M11" t="s">
-        <v>209</v>
-      </c>
-      <c r="N11" t="s">
-        <v>216</v>
-      </c>
-      <c r="O11" t="s">
-        <v>217</v>
-      </c>
-      <c r="P11" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>218</v>
-      </c>
       <c r="R11" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="S11" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="T11" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6788,58 +6828,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D12" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E12" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F12" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G12" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H12" t="s">
+        <v>230</v>
+      </c>
+      <c r="I12" t="s">
+        <v>242</v>
+      </c>
+      <c r="J12" t="s">
+        <v>219</v>
+      </c>
+      <c r="K12" t="s">
+        <v>220</v>
+      </c>
+      <c r="L12" t="s">
+        <v>221</v>
+      </c>
+      <c r="M12" t="s">
+        <v>215</v>
+      </c>
+      <c r="N12" t="s">
+        <v>222</v>
+      </c>
+      <c r="O12" t="s">
+        <v>223</v>
+      </c>
+      <c r="P12" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q12" t="s">
         <v>224</v>
       </c>
-      <c r="I12" t="s">
-        <v>236</v>
-      </c>
-      <c r="J12" t="s">
-        <v>213</v>
-      </c>
-      <c r="K12" t="s">
-        <v>214</v>
-      </c>
-      <c r="L12" t="s">
-        <v>215</v>
-      </c>
-      <c r="M12" t="s">
-        <v>209</v>
-      </c>
-      <c r="N12" t="s">
-        <v>216</v>
-      </c>
-      <c r="O12" t="s">
-        <v>217</v>
-      </c>
-      <c r="P12" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>218</v>
-      </c>
       <c r="R12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="S12" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="T12" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6847,58 +6887,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E13" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F13" t="s">
+        <v>227</v>
+      </c>
+      <c r="G13" t="s">
+        <v>186</v>
+      </c>
+      <c r="H13" t="s">
+        <v>233</v>
+      </c>
+      <c r="I13" t="s">
+        <v>239</v>
+      </c>
+      <c r="J13" t="s">
+        <v>219</v>
+      </c>
+      <c r="K13" t="s">
+        <v>220</v>
+      </c>
+      <c r="L13" t="s">
         <v>221</v>
       </c>
-      <c r="G13" t="s">
-        <v>180</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="M13" t="s">
+        <v>215</v>
+      </c>
+      <c r="N13" t="s">
+        <v>222</v>
+      </c>
+      <c r="O13" t="s">
+        <v>223</v>
+      </c>
+      <c r="P13" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>224</v>
+      </c>
+      <c r="R13" t="s">
+        <v>225</v>
+      </c>
+      <c r="S13" t="s">
+        <v>226</v>
+      </c>
+      <c r="T13" t="s">
         <v>227</v>
-      </c>
-      <c r="I13" t="s">
-        <v>233</v>
-      </c>
-      <c r="J13" t="s">
-        <v>213</v>
-      </c>
-      <c r="K13" t="s">
-        <v>214</v>
-      </c>
-      <c r="L13" t="s">
-        <v>215</v>
-      </c>
-      <c r="M13" t="s">
-        <v>209</v>
-      </c>
-      <c r="N13" t="s">
-        <v>216</v>
-      </c>
-      <c r="O13" t="s">
-        <v>217</v>
-      </c>
-      <c r="P13" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>218</v>
-      </c>
-      <c r="R13" t="s">
-        <v>219</v>
-      </c>
-      <c r="S13" t="s">
-        <v>220</v>
-      </c>
-      <c r="T13" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -6906,58 +6946,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D14" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E14" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F14" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G14" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H14" t="s">
+        <v>233</v>
+      </c>
+      <c r="I14" t="s">
+        <v>242</v>
+      </c>
+      <c r="J14" t="s">
+        <v>219</v>
+      </c>
+      <c r="K14" t="s">
+        <v>220</v>
+      </c>
+      <c r="L14" t="s">
+        <v>221</v>
+      </c>
+      <c r="M14" t="s">
+        <v>215</v>
+      </c>
+      <c r="N14" t="s">
+        <v>222</v>
+      </c>
+      <c r="O14" t="s">
+        <v>223</v>
+      </c>
+      <c r="P14" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>224</v>
+      </c>
+      <c r="R14" t="s">
+        <v>225</v>
+      </c>
+      <c r="S14" t="s">
+        <v>226</v>
+      </c>
+      <c r="T14" t="s">
         <v>227</v>
-      </c>
-      <c r="I14" t="s">
-        <v>236</v>
-      </c>
-      <c r="J14" t="s">
-        <v>213</v>
-      </c>
-      <c r="K14" t="s">
-        <v>214</v>
-      </c>
-      <c r="L14" t="s">
-        <v>215</v>
-      </c>
-      <c r="M14" t="s">
-        <v>209</v>
-      </c>
-      <c r="N14" t="s">
-        <v>216</v>
-      </c>
-      <c r="O14" t="s">
-        <v>217</v>
-      </c>
-      <c r="P14" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>218</v>
-      </c>
-      <c r="R14" t="s">
-        <v>219</v>
-      </c>
-      <c r="S14" t="s">
-        <v>220</v>
-      </c>
-      <c r="T14" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -6965,58 +7005,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D15" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F15" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G15" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H15" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="I15" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="J15" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="K15" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="L15" t="s">
+        <v>221</v>
+      </c>
+      <c r="M15" t="s">
         <v>215</v>
       </c>
-      <c r="M15" t="s">
-        <v>209</v>
-      </c>
       <c r="N15" t="s">
+        <v>222</v>
+      </c>
+      <c r="O15" t="s">
+        <v>223</v>
+      </c>
+      <c r="P15" t="s">
         <v>216</v>
       </c>
-      <c r="O15" t="s">
-        <v>217</v>
-      </c>
-      <c r="P15" t="s">
-        <v>210</v>
-      </c>
       <c r="Q15" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="R15" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="S15" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="T15" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7024,58 +7064,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D16" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E16" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F16" t="s">
+        <v>226</v>
+      </c>
+      <c r="G16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H16" t="s">
+        <v>236</v>
+      </c>
+      <c r="I16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J16" t="s">
+        <v>219</v>
+      </c>
+      <c r="K16" t="s">
         <v>220</v>
       </c>
-      <c r="G16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H16" t="s">
-        <v>230</v>
-      </c>
-      <c r="I16" t="s">
-        <v>236</v>
-      </c>
-      <c r="J16" t="s">
-        <v>213</v>
-      </c>
-      <c r="K16" t="s">
-        <v>214</v>
-      </c>
       <c r="L16" t="s">
+        <v>221</v>
+      </c>
+      <c r="M16" t="s">
         <v>215</v>
       </c>
-      <c r="M16" t="s">
-        <v>209</v>
-      </c>
       <c r="N16" t="s">
+        <v>222</v>
+      </c>
+      <c r="O16" t="s">
+        <v>223</v>
+      </c>
+      <c r="P16" t="s">
         <v>216</v>
       </c>
-      <c r="O16" t="s">
-        <v>217</v>
-      </c>
-      <c r="P16" t="s">
-        <v>210</v>
-      </c>
       <c r="Q16" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="R16" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="S16" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="T16" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -7104,16 +7144,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7127,7 +7167,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7152,16 +7192,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E4" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F4" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7175,10 +7215,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F5" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7186,16 +7226,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F6" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7209,10 +7249,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F7" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7226,10 +7266,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F8" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7243,10 +7283,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F9" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7254,16 +7294,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E10" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F10" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7277,10 +7317,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7294,10 +7334,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F12" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -7330,34 +7370,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="G1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="H1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="I1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="J1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="K1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="L1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="M1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="N1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7368,10 +7408,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7383,7 +7423,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7405,13 +7445,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7422,40 +7462,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D4" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E4" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F4" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G4" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="H4" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="I4" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="J4" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="K4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="L4" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="M4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="N4" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7478,13 +7518,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="L5" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="M5" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7498,22 +7538,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H6" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="L6" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="M6" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7527,22 +7567,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="H7" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="L7" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="M7" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7556,22 +7596,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H8" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="L8" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="M8" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7585,22 +7625,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H9" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="L9" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="M9" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7614,22 +7654,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H10" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="L10" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="M10" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7643,22 +7683,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="H11" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="L11" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="M11" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7672,22 +7712,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="H12" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="L12" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="M12" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7695,31 +7735,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G13" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H13" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="L13" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="M13" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="N13" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7727,10 +7767,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -7739,7 +7779,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7747,10 +7787,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -7759,7 +7799,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7767,10 +7807,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -7779,7 +7819,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7787,19 +7827,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="F17" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="N17" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7807,10 +7847,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -7819,7 +7859,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7827,10 +7867,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -7839,7 +7879,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7847,10 +7887,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -7859,7 +7899,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7867,19 +7907,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E21" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="F21" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="N21" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7887,16 +7927,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -7904,10 +7944,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -7921,10 +7961,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -7938,10 +7978,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -7955,10 +7995,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -7972,10 +8012,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -7989,10 +8029,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8006,10 +8046,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8018,10 +8058,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="N29" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8029,10 +8069,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8046,10 +8086,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8063,10 +8103,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8075,10 +8115,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="N32" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -8114,31 +8154,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D1" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F1" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="G1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="H1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="I1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="J1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="K1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8164,10 +8204,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="I2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8181,34 +8221,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8219,31 +8259,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D4" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E4" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="F4" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G4" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="H4" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="I4" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="J4" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="K4" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8251,7 +8291,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8275,7 +8315,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8283,7 +8323,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8307,7 +8347,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8315,7 +8355,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8339,7 +8379,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8347,7 +8387,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8371,7 +8411,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -8402,16 +8442,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D1" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="E1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8428,7 +8468,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -8441,10 +8481,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8455,13 +8495,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D4" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E4" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8469,7 +8509,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8478,7 +8518,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8486,7 +8526,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -8495,7 +8535,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8503,7 +8543,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -8512,7 +8552,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8520,7 +8560,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8529,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8567,40 +8607,40 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C1" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D1" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="E1" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F1" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="G1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="H1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="I1" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="J1" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="K1" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="L1" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="M1" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -8614,16 +8654,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -8649,40 +8689,40 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="I3" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="J3" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="K3" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="L3" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="M3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8690,54 +8730,54 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C4" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E4" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="F4" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="G4" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="H4" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="I4" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="J4" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="K4" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="L4" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="M4" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D5" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8749,36 +8789,36 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="I5" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="J5" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="K5" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="L5" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="M5" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D6" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8790,36 +8830,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="I6" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="J6" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="K6" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="L6" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M6" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D7" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8831,36 +8871,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="I7" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="J7" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="K7" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L7" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="M7" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D8" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8872,36 +8912,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="I8" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="J8" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="K8" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="L8" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="M8" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D9" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8913,36 +8953,36 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="I9" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="J9" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="K9" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="L9" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="M9" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D10" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8954,36 +8994,36 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="I10" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="J10" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="K10" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="L10" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="M10" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D11" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -8995,36 +9035,36 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="I11" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="J11" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="K11" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="L11" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="M11" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D12" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -9036,36 +9076,36 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="I12" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="J12" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="K12" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="L12" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="M12" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D13" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -9077,36 +9117,36 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="I13" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="J13" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="K13" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L13" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="M13" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D14" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -9118,36 +9158,36 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="I14" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="J14" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="K14" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="L14" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="M14" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D15" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -9159,39 +9199,39 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="I15" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="J15" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="K15" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="L15" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="M15" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D16" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E16" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -9200,39 +9240,39 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="I16" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="J16" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="K16" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="L16" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="M16" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D17" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E17" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -9241,39 +9281,39 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="I17" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="J17" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="K17" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="L17" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="M17" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D18" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E18" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -9282,39 +9322,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="I18" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="J18" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="K18" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="L18" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="M18" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D19" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E19" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -9323,39 +9363,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="I19" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="J19" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="K19" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="L19" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="M19" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D20" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E20" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -9364,39 +9404,39 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="I20" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="J20" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="K20" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="L20" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="M20" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="D21" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E21" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -9405,39 +9445,39 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="I21" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="J21" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="K21" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L21" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="M21" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="D22" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E22" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -9446,39 +9486,39 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="I22" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="J22" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="K22" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="L22" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M22" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D23" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E23" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -9487,39 +9527,39 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="I23" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="J23" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="K23" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="L23" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="M23" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D24" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E24" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -9528,39 +9568,39 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="I24" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="J24" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="K24" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="L24" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="M24" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D25" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E25" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -9569,22 +9609,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="I25" t="s">
         <v>52</v>
       </c>
       <c r="J25" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="K25" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="L25" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="M25" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -9592,10 +9632,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="D26" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -9607,22 +9647,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="I26" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="J26" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="K26" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="L26" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="M26" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -9630,13 +9670,13 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D27" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="E27" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -9645,36 +9685,36 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="I27" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="J27" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="K27" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="L27" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="M27" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D28" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -9686,36 +9726,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="I28" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="J28" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K28" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="L28" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="M28" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="D29" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -9727,36 +9767,36 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="I29" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="J29" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="K29" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="L29" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="M29" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D30" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="E30" t="s">
         <v>2</v>
@@ -9768,39 +9808,39 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="I30" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="J30" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="K30" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="L30" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="M30" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="D31" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="E31" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -9809,22 +9849,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="I31" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="J31" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="K31" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="L31" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="M31" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -9832,13 +9872,13 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="D32" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E32" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -9847,22 +9887,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="I32" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="J32" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="K32" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="L32" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="M32" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak2/xlsx/Main.xlsx
+++ b/luban-excels/bak2/xlsx/Main.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="862">
   <si>
     <t>Dog</t>
   </si>
@@ -536,22 +536,13 @@
     <t>统计时，玩家实际行为乘以倍率作为统计值记录，例如玩家获得1个筹码，倍率是10的话，记为10个筹码</t>
   </si>
   <si>
-    <t>BlindBoxBacklogClaimDelaySeconds</t>
-  </si>
-  <si>
-    <t>积压盲盒展示时短间隔时间</t>
-  </si>
-  <si>
-    <t>秒，实际使用时需要受到BlindBoxTimeScale影响，为了不让玩家对于盲盒间隔的心里预期剧烈变化因此设计了该值</t>
-  </si>
-  <si>
-    <t>BlindBoxPostNewbieDelaySeconds</t>
-  </si>
-  <si>
-    <t>新手与正式盲盒的间隔时间</t>
-  </si>
-  <si>
-    <t>秒，新手阶段结束后与第一个正式盲盒的间隔时间</t>
+    <t>BlindBoxLoopIntervalSeconds</t>
+  </si>
+  <si>
+    <t>正常阶段盲盒展示间隔</t>
+  </si>
+  <si>
+    <t>秒；第 12 个新手奖励入账后，按此基础间隔产生展示点并触发循环 Steam 掉落检查；实际时长受 BlindBoxWaitDurationMultiplier 影响</t>
   </si>
   <si>
     <t>LinkTreeVisibleBannerCount</t>
@@ -560,7 +551,7 @@
     <t>LinkTree最佳显示条目数量</t>
   </si>
   <si>
-    <t>未领取奖励的条目和固定条目数量之和不足该值只，以已领取奖励的条目填充占位</t>
+    <t>未领取奖励的条目和固定条目数量之和不足该值时，以已领取奖励的条目填充占位</t>
   </si>
   <si>
     <t>SteamPlaytimeDropLeadSeconds</t>
@@ -569,7 +560,7 @@
     <t>Steam提前准备盲盒的秒数</t>
   </si>
   <si>
-    <t>掉落提前秒数Steam游玩时间掉落相对本地盲盒展示时间提前请求的秒数，用于避开服务器计时边界。正式配置时改为60</t>
+    <t>仅用于前 12 个一次性游玩投放；相对本地盲盒展示时间提前请求，用于避开 Steam 分钟计时边界</t>
   </si>
   <si>
     <t>IconName</t>
@@ -4206,28 +4197,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D1" t="s">
+        <v>655</v>
+      </c>
+      <c r="E1" t="s">
         <v>656</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>657</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>658</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>659</v>
       </c>
-      <c r="F1" t="s">
-        <v>660</v>
-      </c>
-      <c r="G1" t="s">
-        <v>661</v>
-      </c>
-      <c r="H1" t="s">
-        <v>662</v>
-      </c>
       <c r="I1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4244,16 +4235,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4264,28 +4255,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4293,1333 +4284,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>670</v>
+      </c>
+      <c r="C4" t="s">
+        <v>671</v>
+      </c>
+      <c r="D4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" t="s">
+        <v>672</v>
+      </c>
+      <c r="F4" t="s">
         <v>673</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>674</v>
       </c>
-      <c r="D4" t="s">
-        <v>260</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>675</v>
       </c>
-      <c r="F4" t="s">
-        <v>676</v>
-      </c>
-      <c r="G4" t="s">
-        <v>677</v>
-      </c>
-      <c r="H4" t="s">
-        <v>678</v>
-      </c>
       <c r="I4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
+        <v>676</v>
+      </c>
+      <c r="D5" t="s">
+        <v>677</v>
+      </c>
+      <c r="E5" t="s">
+        <v>678</v>
+      </c>
+      <c r="F5" t="s">
         <v>679</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>680</v>
-      </c>
-      <c r="E5" t="s">
-        <v>681</v>
-      </c>
-      <c r="F5" t="s">
-        <v>682</v>
-      </c>
-      <c r="G5" t="s">
-        <v>683</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>682</v>
+      </c>
+      <c r="D6" t="s">
+        <v>683</v>
+      </c>
+      <c r="E6" t="s">
+        <v>684</v>
+      </c>
+      <c r="F6" t="s">
+        <v>679</v>
+      </c>
+      <c r="G6" t="s">
         <v>685</v>
-      </c>
-      <c r="D6" t="s">
-        <v>686</v>
-      </c>
-      <c r="E6" t="s">
-        <v>687</v>
-      </c>
-      <c r="F6" t="s">
-        <v>682</v>
-      </c>
-      <c r="G6" t="s">
-        <v>688</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D7" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E7" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F7" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G7" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D8" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E8" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F8" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G8" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D9" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E9" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F9" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G9" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
+        <v>699</v>
+      </c>
+      <c r="D10" t="s">
+        <v>700</v>
+      </c>
+      <c r="E10" t="s">
+        <v>701</v>
+      </c>
+      <c r="F10" t="s">
+        <v>679</v>
+      </c>
+      <c r="G10" t="s">
         <v>702</v>
-      </c>
-      <c r="D10" t="s">
-        <v>703</v>
-      </c>
-      <c r="E10" t="s">
-        <v>704</v>
-      </c>
-      <c r="F10" t="s">
-        <v>682</v>
-      </c>
-      <c r="G10" t="s">
-        <v>705</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D11" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E11" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F11" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G11" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D12" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E12" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F12" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G12" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D13" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E13" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F13" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G13" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E14" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F14" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G14" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D15" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E15" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F15" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G15" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D16" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E16" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F16" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G16" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D17" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E17" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F17" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G17" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D18" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="E18" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F18" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G18" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D19" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E19" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F19" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G19" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D20" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="E20" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F20" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G20" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D21" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="E21" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F21" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G21" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D22" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E22" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F22" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G22" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D23" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F23" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G23" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D24" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="E24" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F24" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G24" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D25" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E25" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F25" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G25" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D26" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E26" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F26" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G26" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D27" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E27" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F27" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G27" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D28" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E28" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F28" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G28" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D29" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E29" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F29" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G29" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D30" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E30" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F30" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G30" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D31" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E31" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F31" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G31" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D32" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="E32" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F32" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G32" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D33" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="E33" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F33" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G33" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D34" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="E34" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F34" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G34" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D35" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="E35" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F35" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G35" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D36" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="E36" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F36" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G36" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="D37" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="E37" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F37" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G37" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D38" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="E38" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F38" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G38" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D39" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="E39" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F39" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G39" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D40" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E40" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F40" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G40" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D41" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E41" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F41" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G41" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D42" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E42" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F42" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G42" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="D43" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E43" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F43" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G43" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D44" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="E44" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F44" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G44" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D45" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="E45" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F45" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G45" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D46" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="E46" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F46" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G46" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D47" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="E47" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F47" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G47" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D48" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="E48" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F48" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G48" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="D49" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="E49" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F49" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G49" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5627,25 +5618,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="D50" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="E50" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F50" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G50" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5653,25 +5644,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
+        <v>857</v>
+      </c>
+      <c r="D51" t="s">
+        <v>858</v>
+      </c>
+      <c r="E51" t="s">
+        <v>701</v>
+      </c>
+      <c r="F51" t="s">
+        <v>859</v>
+      </c>
+      <c r="G51" t="s">
         <v>860</v>
-      </c>
-      <c r="D51" t="s">
-        <v>861</v>
-      </c>
-      <c r="E51" t="s">
-        <v>704</v>
-      </c>
-      <c r="F51" t="s">
-        <v>862</v>
-      </c>
-      <c r="G51" t="s">
-        <v>863</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -6120,7 +6111,7 @@
         <v>158</v>
       </c>
       <c r="D6" s="2">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>168</v>
@@ -6134,10 +6125,10 @@
         <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="D7" s="2">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
         <v>171</v>
@@ -6154,28 +6145,18 @@
         <v>107</v>
       </c>
       <c r="D8" s="2">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="2">
-        <v>60</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2"/>
@@ -6223,55 +6204,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" t="s">
         <v>181</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" t="s">
         <v>182</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" t="s">
         <v>183</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>184</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>185</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>186</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>187</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>188</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>189</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>190</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>191</v>
-      </c>
-      <c r="R1" t="s">
-        <v>192</v>
-      </c>
-      <c r="S1" t="s">
-        <v>193</v>
-      </c>
-      <c r="T1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6342,10 +6323,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6359,55 +6340,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" t="s">
         <v>196</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>197</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>198</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>199</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>200</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>201</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>202</v>
       </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>203</v>
       </c>
-      <c r="L4" t="s">
+      <c r="O4" t="s">
         <v>204</v>
       </c>
-      <c r="M4" t="s">
+      <c r="P4" t="s">
         <v>205</v>
       </c>
-      <c r="N4" t="s">
+      <c r="Q4" t="s">
         <v>206</v>
       </c>
-      <c r="O4" t="s">
+      <c r="R4" t="s">
         <v>207</v>
       </c>
-      <c r="P4" t="s">
+      <c r="S4" t="s">
         <v>208</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="T4" t="s">
         <v>209</v>
-      </c>
-      <c r="R4" t="s">
-        <v>210</v>
-      </c>
-      <c r="S4" t="s">
-        <v>211</v>
-      </c>
-      <c r="T4" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6415,58 +6396,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" t="s">
         <v>213</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H5" t="s">
         <v>214</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
         <v>215</v>
       </c>
-      <c r="F5" t="s">
+      <c r="J5" t="s">
         <v>216</v>
       </c>
-      <c r="G5" t="s">
-        <v>186</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>217</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>218</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
+        <v>212</v>
+      </c>
+      <c r="N5" t="s">
         <v>219</v>
       </c>
-      <c r="K5" t="s">
+      <c r="O5" t="s">
         <v>220</v>
       </c>
-      <c r="L5" t="s">
+      <c r="P5" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q5" t="s">
         <v>221</v>
       </c>
-      <c r="M5" t="s">
-        <v>215</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="R5" t="s">
         <v>222</v>
       </c>
-      <c r="O5" t="s">
+      <c r="S5" t="s">
         <v>223</v>
       </c>
-      <c r="P5" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q5" t="s">
+      <c r="T5" t="s">
         <v>224</v>
-      </c>
-      <c r="R5" t="s">
-        <v>225</v>
-      </c>
-      <c r="S5" t="s">
-        <v>226</v>
-      </c>
-      <c r="T5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -6474,58 +6455,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I6" t="s">
         <v>215</v>
       </c>
-      <c r="F6" t="s">
+      <c r="J6" t="s">
+        <v>216</v>
+      </c>
+      <c r="K6" t="s">
+        <v>217</v>
+      </c>
+      <c r="L6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" t="s">
+        <v>212</v>
+      </c>
+      <c r="N6" t="s">
+        <v>219</v>
+      </c>
+      <c r="O6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P6" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>221</v>
+      </c>
+      <c r="R6" t="s">
+        <v>222</v>
+      </c>
+      <c r="S6" t="s">
+        <v>223</v>
+      </c>
+      <c r="T6" t="s">
         <v>224</v>
-      </c>
-      <c r="G6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H6" t="s">
-        <v>230</v>
-      </c>
-      <c r="I6" t="s">
-        <v>218</v>
-      </c>
-      <c r="J6" t="s">
-        <v>219</v>
-      </c>
-      <c r="K6" t="s">
-        <v>220</v>
-      </c>
-      <c r="L6" t="s">
-        <v>221</v>
-      </c>
-      <c r="M6" t="s">
-        <v>215</v>
-      </c>
-      <c r="N6" t="s">
-        <v>222</v>
-      </c>
-      <c r="O6" t="s">
-        <v>223</v>
-      </c>
-      <c r="P6" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>224</v>
-      </c>
-      <c r="R6" t="s">
-        <v>225</v>
-      </c>
-      <c r="S6" t="s">
-        <v>226</v>
-      </c>
-      <c r="T6" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6533,58 +6514,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I7" t="s">
         <v>215</v>
       </c>
-      <c r="F7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G7" t="s">
-        <v>186</v>
-      </c>
-      <c r="H7" t="s">
-        <v>233</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
+        <v>216</v>
+      </c>
+      <c r="K7" t="s">
+        <v>217</v>
+      </c>
+      <c r="L7" t="s">
         <v>218</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
+        <v>212</v>
+      </c>
+      <c r="N7" t="s">
         <v>219</v>
       </c>
-      <c r="K7" t="s">
+      <c r="O7" t="s">
         <v>220</v>
       </c>
-      <c r="L7" t="s">
+      <c r="P7" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q7" t="s">
         <v>221</v>
       </c>
-      <c r="M7" t="s">
-        <v>215</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="R7" t="s">
         <v>222</v>
       </c>
-      <c r="O7" t="s">
+      <c r="S7" t="s">
         <v>223</v>
       </c>
-      <c r="P7" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="T7" t="s">
         <v>224</v>
-      </c>
-      <c r="R7" t="s">
-        <v>225</v>
-      </c>
-      <c r="S7" t="s">
-        <v>226</v>
-      </c>
-      <c r="T7" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -6592,58 +6573,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E8" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" t="s">
+        <v>220</v>
+      </c>
+      <c r="G8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" t="s">
+        <v>233</v>
+      </c>
+      <c r="I8" t="s">
+        <v>215</v>
+      </c>
+      <c r="J8" t="s">
+        <v>216</v>
+      </c>
+      <c r="K8" t="s">
+        <v>217</v>
+      </c>
+      <c r="L8" t="s">
+        <v>218</v>
+      </c>
+      <c r="M8" t="s">
+        <v>212</v>
+      </c>
+      <c r="N8" t="s">
+        <v>219</v>
+      </c>
+      <c r="O8" t="s">
+        <v>220</v>
+      </c>
+      <c r="P8" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>221</v>
+      </c>
+      <c r="R8" t="s">
         <v>222</v>
       </c>
-      <c r="F8" t="s">
+      <c r="S8" t="s">
         <v>223</v>
       </c>
-      <c r="G8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H8" t="s">
-        <v>236</v>
-      </c>
-      <c r="I8" t="s">
-        <v>218</v>
-      </c>
-      <c r="J8" t="s">
-        <v>219</v>
-      </c>
-      <c r="K8" t="s">
-        <v>220</v>
-      </c>
-      <c r="L8" t="s">
-        <v>221</v>
-      </c>
-      <c r="M8" t="s">
-        <v>215</v>
-      </c>
-      <c r="N8" t="s">
-        <v>222</v>
-      </c>
-      <c r="O8" t="s">
-        <v>223</v>
-      </c>
-      <c r="P8" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q8" t="s">
+      <c r="T8" t="s">
         <v>224</v>
-      </c>
-      <c r="R8" t="s">
-        <v>225</v>
-      </c>
-      <c r="S8" t="s">
-        <v>226</v>
-      </c>
-      <c r="T8" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6651,58 +6632,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H9" t="s">
+        <v>214</v>
+      </c>
+      <c r="I9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J9" t="s">
+        <v>216</v>
+      </c>
+      <c r="K9" t="s">
         <v>217</v>
       </c>
-      <c r="I9" t="s">
-        <v>239</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
+        <v>218</v>
+      </c>
+      <c r="M9" t="s">
+        <v>212</v>
+      </c>
+      <c r="N9" t="s">
         <v>219</v>
       </c>
-      <c r="K9" t="s">
+      <c r="O9" t="s">
         <v>220</v>
       </c>
-      <c r="L9" t="s">
+      <c r="P9" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q9" t="s">
         <v>221</v>
       </c>
-      <c r="M9" t="s">
-        <v>215</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="R9" t="s">
         <v>222</v>
       </c>
-      <c r="O9" t="s">
+      <c r="S9" t="s">
         <v>223</v>
       </c>
-      <c r="P9" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q9" t="s">
+      <c r="T9" t="s">
         <v>224</v>
-      </c>
-      <c r="R9" t="s">
-        <v>225</v>
-      </c>
-      <c r="S9" t="s">
-        <v>226</v>
-      </c>
-      <c r="T9" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6710,58 +6691,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F10" t="s">
+        <v>213</v>
+      </c>
+      <c r="G10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" t="s">
+        <v>239</v>
+      </c>
+      <c r="J10" t="s">
+        <v>216</v>
+      </c>
+      <c r="K10" t="s">
+        <v>217</v>
+      </c>
+      <c r="L10" t="s">
+        <v>218</v>
+      </c>
+      <c r="M10" t="s">
+        <v>212</v>
+      </c>
+      <c r="N10" t="s">
+        <v>219</v>
+      </c>
+      <c r="O10" t="s">
+        <v>220</v>
+      </c>
+      <c r="P10" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>221</v>
+      </c>
+      <c r="R10" t="s">
         <v>222</v>
       </c>
-      <c r="F10" t="s">
-        <v>216</v>
-      </c>
-      <c r="G10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H10" t="s">
-        <v>217</v>
-      </c>
-      <c r="I10" t="s">
-        <v>242</v>
-      </c>
-      <c r="J10" t="s">
-        <v>219</v>
-      </c>
-      <c r="K10" t="s">
-        <v>220</v>
-      </c>
-      <c r="L10" t="s">
-        <v>221</v>
-      </c>
-      <c r="M10" t="s">
-        <v>215</v>
-      </c>
-      <c r="N10" t="s">
-        <v>222</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="S10" t="s">
         <v>223</v>
       </c>
-      <c r="P10" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q10" t="s">
+      <c r="T10" t="s">
         <v>224</v>
-      </c>
-      <c r="R10" t="s">
-        <v>225</v>
-      </c>
-      <c r="S10" t="s">
-        <v>226</v>
-      </c>
-      <c r="T10" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6769,58 +6750,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D11" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F11" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" t="s">
         <v>227</v>
       </c>
-      <c r="G11" t="s">
-        <v>186</v>
-      </c>
-      <c r="H11" t="s">
-        <v>230</v>
-      </c>
       <c r="I11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J11" t="s">
+        <v>216</v>
+      </c>
+      <c r="K11" t="s">
+        <v>217</v>
+      </c>
+      <c r="L11" t="s">
+        <v>218</v>
+      </c>
+      <c r="M11" t="s">
+        <v>212</v>
+      </c>
+      <c r="N11" t="s">
         <v>219</v>
       </c>
-      <c r="K11" t="s">
+      <c r="O11" t="s">
         <v>220</v>
       </c>
-      <c r="L11" t="s">
+      <c r="P11" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q11" t="s">
         <v>221</v>
       </c>
-      <c r="M11" t="s">
-        <v>215</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="R11" t="s">
         <v>222</v>
       </c>
-      <c r="O11" t="s">
+      <c r="S11" t="s">
         <v>223</v>
       </c>
-      <c r="P11" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q11" t="s">
+      <c r="T11" t="s">
         <v>224</v>
-      </c>
-      <c r="R11" t="s">
-        <v>225</v>
-      </c>
-      <c r="S11" t="s">
-        <v>226</v>
-      </c>
-      <c r="T11" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6828,58 +6809,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F12" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" t="s">
+        <v>183</v>
+      </c>
+      <c r="H12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I12" t="s">
+        <v>239</v>
+      </c>
+      <c r="J12" t="s">
         <v>216</v>
       </c>
-      <c r="G12" t="s">
-        <v>186</v>
-      </c>
-      <c r="H12" t="s">
-        <v>230</v>
-      </c>
-      <c r="I12" t="s">
-        <v>242</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
+        <v>217</v>
+      </c>
+      <c r="L12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M12" t="s">
+        <v>212</v>
+      </c>
+      <c r="N12" t="s">
         <v>219</v>
       </c>
-      <c r="K12" t="s">
+      <c r="O12" t="s">
         <v>220</v>
       </c>
-      <c r="L12" t="s">
+      <c r="P12" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q12" t="s">
         <v>221</v>
       </c>
-      <c r="M12" t="s">
-        <v>215</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="R12" t="s">
         <v>222</v>
       </c>
-      <c r="O12" t="s">
+      <c r="S12" t="s">
         <v>223</v>
       </c>
-      <c r="P12" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q12" t="s">
+      <c r="T12" t="s">
         <v>224</v>
-      </c>
-      <c r="R12" t="s">
-        <v>225</v>
-      </c>
-      <c r="S12" t="s">
-        <v>226</v>
-      </c>
-      <c r="T12" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6887,58 +6868,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E13" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F13" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G13" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H13" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I13" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J13" t="s">
+        <v>216</v>
+      </c>
+      <c r="K13" t="s">
+        <v>217</v>
+      </c>
+      <c r="L13" t="s">
+        <v>218</v>
+      </c>
+      <c r="M13" t="s">
+        <v>212</v>
+      </c>
+      <c r="N13" t="s">
         <v>219</v>
       </c>
-      <c r="K13" t="s">
+      <c r="O13" t="s">
         <v>220</v>
       </c>
-      <c r="L13" t="s">
+      <c r="P13" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q13" t="s">
         <v>221</v>
       </c>
-      <c r="M13" t="s">
-        <v>215</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="R13" t="s">
         <v>222</v>
       </c>
-      <c r="O13" t="s">
+      <c r="S13" t="s">
         <v>223</v>
       </c>
-      <c r="P13" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q13" t="s">
+      <c r="T13" t="s">
         <v>224</v>
-      </c>
-      <c r="R13" t="s">
-        <v>225</v>
-      </c>
-      <c r="S13" t="s">
-        <v>226</v>
-      </c>
-      <c r="T13" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -6946,58 +6927,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D14" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E14" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F14" t="s">
+        <v>213</v>
+      </c>
+      <c r="G14" t="s">
+        <v>183</v>
+      </c>
+      <c r="H14" t="s">
+        <v>230</v>
+      </c>
+      <c r="I14" t="s">
+        <v>239</v>
+      </c>
+      <c r="J14" t="s">
         <v>216</v>
       </c>
-      <c r="G14" t="s">
-        <v>186</v>
-      </c>
-      <c r="H14" t="s">
-        <v>233</v>
-      </c>
-      <c r="I14" t="s">
-        <v>242</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
+        <v>217</v>
+      </c>
+      <c r="L14" t="s">
+        <v>218</v>
+      </c>
+      <c r="M14" t="s">
+        <v>212</v>
+      </c>
+      <c r="N14" t="s">
         <v>219</v>
       </c>
-      <c r="K14" t="s">
+      <c r="O14" t="s">
         <v>220</v>
       </c>
-      <c r="L14" t="s">
+      <c r="P14" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q14" t="s">
         <v>221</v>
       </c>
-      <c r="M14" t="s">
-        <v>215</v>
-      </c>
-      <c r="N14" t="s">
+      <c r="R14" t="s">
         <v>222</v>
       </c>
-      <c r="O14" t="s">
+      <c r="S14" t="s">
         <v>223</v>
       </c>
-      <c r="P14" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q14" t="s">
+      <c r="T14" t="s">
         <v>224</v>
-      </c>
-      <c r="R14" t="s">
-        <v>225</v>
-      </c>
-      <c r="S14" t="s">
-        <v>226</v>
-      </c>
-      <c r="T14" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -7005,58 +6986,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D15" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E15" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F15" t="s">
+        <v>213</v>
+      </c>
+      <c r="G15" t="s">
+        <v>183</v>
+      </c>
+      <c r="H15" t="s">
+        <v>233</v>
+      </c>
+      <c r="I15" t="s">
+        <v>236</v>
+      </c>
+      <c r="J15" t="s">
         <v>216</v>
       </c>
-      <c r="G15" t="s">
-        <v>186</v>
-      </c>
-      <c r="H15" t="s">
-        <v>236</v>
-      </c>
-      <c r="I15" t="s">
-        <v>239</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L15" t="s">
+        <v>218</v>
+      </c>
+      <c r="M15" t="s">
+        <v>212</v>
+      </c>
+      <c r="N15" t="s">
         <v>219</v>
       </c>
-      <c r="K15" t="s">
+      <c r="O15" t="s">
         <v>220</v>
       </c>
-      <c r="L15" t="s">
+      <c r="P15" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q15" t="s">
         <v>221</v>
       </c>
-      <c r="M15" t="s">
-        <v>215</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="R15" t="s">
         <v>222</v>
       </c>
-      <c r="O15" t="s">
+      <c r="S15" t="s">
         <v>223</v>
       </c>
-      <c r="P15" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q15" t="s">
+      <c r="T15" t="s">
         <v>224</v>
-      </c>
-      <c r="R15" t="s">
-        <v>225</v>
-      </c>
-      <c r="S15" t="s">
-        <v>226</v>
-      </c>
-      <c r="T15" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7064,58 +7045,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F16" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G16" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J16" t="s">
+        <v>216</v>
+      </c>
+      <c r="K16" t="s">
+        <v>217</v>
+      </c>
+      <c r="L16" t="s">
+        <v>218</v>
+      </c>
+      <c r="M16" t="s">
+        <v>212</v>
+      </c>
+      <c r="N16" t="s">
         <v>219</v>
       </c>
-      <c r="K16" t="s">
+      <c r="O16" t="s">
         <v>220</v>
       </c>
-      <c r="L16" t="s">
+      <c r="P16" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q16" t="s">
         <v>221</v>
       </c>
-      <c r="M16" t="s">
-        <v>215</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="R16" t="s">
         <v>222</v>
       </c>
-      <c r="O16" t="s">
+      <c r="S16" t="s">
         <v>223</v>
       </c>
-      <c r="P16" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q16" t="s">
+      <c r="T16" t="s">
         <v>224</v>
-      </c>
-      <c r="R16" t="s">
-        <v>225</v>
-      </c>
-      <c r="S16" t="s">
-        <v>226</v>
-      </c>
-      <c r="T16" t="s">
-        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -7144,16 +7125,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F1" t="s">
         <v>255</v>
-      </c>
-      <c r="D1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7167,7 +7148,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7192,16 +7173,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F4" t="s">
         <v>260</v>
-      </c>
-      <c r="D4" t="s">
-        <v>261</v>
-      </c>
-      <c r="E4" t="s">
-        <v>262</v>
-      </c>
-      <c r="F4" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7215,10 +7196,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7226,16 +7207,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7249,10 +7230,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7266,10 +7247,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7283,10 +7264,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7294,16 +7275,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
+        <v>272</v>
+      </c>
+      <c r="D10" t="s">
+        <v>273</v>
+      </c>
+      <c r="E10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F10" t="s">
         <v>275</v>
-      </c>
-      <c r="D10" t="s">
-        <v>276</v>
-      </c>
-      <c r="E10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F10" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7317,10 +7298,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7334,10 +7315,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F12" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -7370,34 +7351,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H1" t="s">
         <v>283</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>284</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>285</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>286</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>287</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>288</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>289</v>
-      </c>
-      <c r="L1" t="s">
-        <v>290</v>
-      </c>
-      <c r="M1" t="s">
-        <v>291</v>
-      </c>
-      <c r="N1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7408,10 +7389,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7423,7 +7404,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7445,13 +7426,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7462,40 +7443,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F4" t="s">
+        <v>296</v>
+      </c>
+      <c r="G4" t="s">
         <v>298</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>299</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>300</v>
       </c>
-      <c r="F4" t="s">
-        <v>299</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>301</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>302</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>303</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
+        <v>201</v>
+      </c>
+      <c r="N4" t="s">
         <v>304</v>
-      </c>
-      <c r="K4" t="s">
-        <v>305</v>
-      </c>
-      <c r="L4" t="s">
-        <v>306</v>
-      </c>
-      <c r="M4" t="s">
-        <v>204</v>
-      </c>
-      <c r="N4" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7518,13 +7499,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7538,22 +7519,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H6" t="s">
         <v>187</v>
-      </c>
-      <c r="H6" t="s">
-        <v>190</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7567,22 +7548,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7596,22 +7577,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H8" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7625,22 +7606,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7654,22 +7635,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7683,22 +7664,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L11" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7712,22 +7693,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H12" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="L12" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M12" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7735,31 +7716,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G13" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" t="s">
         <v>187</v>
-      </c>
-      <c r="H13" t="s">
-        <v>190</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M13" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N13" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7767,10 +7748,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -7779,7 +7760,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7787,10 +7768,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -7799,7 +7780,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7807,10 +7788,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -7819,7 +7800,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7827,19 +7808,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="F17" t="s">
         <v>324</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="N17" t="s">
         <v>325</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="F17" t="s">
-        <v>327</v>
-      </c>
-      <c r="N17" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7847,10 +7828,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -7859,7 +7840,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7867,10 +7848,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -7879,7 +7860,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7887,10 +7868,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -7899,7 +7880,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7907,19 +7888,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E21" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F21" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="N21" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7927,16 +7908,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -7944,10 +7925,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -7961,10 +7942,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -7978,10 +7959,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -7995,10 +7976,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -8012,10 +7993,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -8029,10 +8010,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8046,10 +8027,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8058,10 +8039,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N29" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8069,10 +8050,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8086,10 +8067,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8103,10 +8084,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8115,10 +8096,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N32" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -8154,31 +8135,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F1" t="s">
         <v>363</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>364</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1" t="s">
         <v>365</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>366</v>
       </c>
-      <c r="G1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H1" t="s">
-        <v>283</v>
-      </c>
-      <c r="I1" t="s">
-        <v>368</v>
-      </c>
-      <c r="J1" t="s">
-        <v>369</v>
-      </c>
       <c r="K1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8204,10 +8185,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8221,34 +8202,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8259,31 +8240,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F4" t="s">
         <v>379</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>380</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>381</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>382</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>383</v>
       </c>
-      <c r="H4" t="s">
-        <v>384</v>
-      </c>
-      <c r="I4" t="s">
-        <v>385</v>
-      </c>
-      <c r="J4" t="s">
-        <v>386</v>
-      </c>
       <c r="K4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8291,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8315,7 +8296,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8323,7 +8304,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8347,7 +8328,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8355,7 +8336,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8379,7 +8360,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8387,7 +8368,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8411,7 +8392,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -8442,16 +8423,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8468,7 +8449,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -8481,10 +8462,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8495,13 +8476,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8509,7 +8490,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8518,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8526,7 +8507,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -8535,7 +8516,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8543,7 +8524,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -8552,7 +8533,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8560,7 +8541,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8569,7 +8550,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8607,40 +8588,40 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E1" t="s">
         <v>409</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>410</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>411</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I1" t="s">
         <v>412</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>413</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>414</v>
       </c>
-      <c r="H1" t="s">
-        <v>292</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>415</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>416</v>
-      </c>
-      <c r="K1" t="s">
-        <v>417</v>
-      </c>
-      <c r="L1" t="s">
-        <v>418</v>
-      </c>
-      <c r="M1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -8654,16 +8635,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="G2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -8689,40 +8670,40 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" t="s">
         <v>426</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="K3" t="s">
         <v>428</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
         <v>429</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>430</v>
-      </c>
-      <c r="K3" t="s">
-        <v>431</v>
-      </c>
-      <c r="L3" t="s">
-        <v>432</v>
-      </c>
-      <c r="M3" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8730,54 +8711,54 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C4" t="s">
+        <v>432</v>
+      </c>
+      <c r="D4" t="s">
+        <v>433</v>
+      </c>
+      <c r="E4" t="s">
         <v>434</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>435</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>436</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
+        <v>304</v>
+      </c>
+      <c r="I4" t="s">
         <v>437</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>438</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4" t="s">
         <v>439</v>
       </c>
-      <c r="H4" t="s">
-        <v>307</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>440</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>441</v>
-      </c>
-      <c r="K4" t="s">
-        <v>442</v>
-      </c>
-      <c r="L4" t="s">
-        <v>443</v>
-      </c>
-      <c r="M4" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D5" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8789,36 +8770,36 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
+        <v>444</v>
+      </c>
+      <c r="I5" t="s">
+        <v>445</v>
+      </c>
+      <c r="J5" t="s">
+        <v>446</v>
+      </c>
+      <c r="K5" t="s">
         <v>447</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>448</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>449</v>
-      </c>
-      <c r="K5" t="s">
-        <v>450</v>
-      </c>
-      <c r="L5" t="s">
-        <v>451</v>
-      </c>
-      <c r="M5" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D6" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8830,36 +8811,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
+        <v>451</v>
+      </c>
+      <c r="I6" t="s">
+        <v>452</v>
+      </c>
+      <c r="J6" t="s">
+        <v>453</v>
+      </c>
+      <c r="K6" t="s">
         <v>454</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>455</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>456</v>
-      </c>
-      <c r="K6" t="s">
-        <v>457</v>
-      </c>
-      <c r="L6" t="s">
-        <v>458</v>
-      </c>
-      <c r="M6" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D7" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8871,36 +8852,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
+        <v>458</v>
+      </c>
+      <c r="I7" t="s">
+        <v>459</v>
+      </c>
+      <c r="J7" t="s">
+        <v>460</v>
+      </c>
+      <c r="K7" t="s">
         <v>461</v>
       </c>
-      <c r="I7" t="s">
+      <c r="L7" t="s">
         <v>462</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
         <v>463</v>
-      </c>
-      <c r="K7" t="s">
-        <v>464</v>
-      </c>
-      <c r="L7" t="s">
-        <v>465</v>
-      </c>
-      <c r="M7" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D8" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8912,36 +8893,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="I8" t="s">
+        <v>466</v>
+      </c>
+      <c r="J8" t="s">
+        <v>467</v>
+      </c>
+      <c r="K8" t="s">
         <v>468</v>
       </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
         <v>469</v>
       </c>
-      <c r="J8" t="s">
+      <c r="M8" t="s">
         <v>470</v>
-      </c>
-      <c r="K8" t="s">
-        <v>471</v>
-      </c>
-      <c r="L8" t="s">
-        <v>472</v>
-      </c>
-      <c r="M8" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8953,36 +8934,36 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
+        <v>472</v>
+      </c>
+      <c r="I9" t="s">
+        <v>473</v>
+      </c>
+      <c r="J9" t="s">
+        <v>474</v>
+      </c>
+      <c r="K9" t="s">
         <v>475</v>
       </c>
-      <c r="I9" t="s">
+      <c r="L9" t="s">
         <v>476</v>
       </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>477</v>
-      </c>
-      <c r="K9" t="s">
-        <v>478</v>
-      </c>
-      <c r="L9" t="s">
-        <v>479</v>
-      </c>
-      <c r="M9" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D10" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8994,36 +8975,36 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
+        <v>479</v>
+      </c>
+      <c r="I10" t="s">
+        <v>480</v>
+      </c>
+      <c r="J10" t="s">
+        <v>481</v>
+      </c>
+      <c r="K10" t="s">
         <v>482</v>
       </c>
-      <c r="I10" t="s">
+      <c r="L10" t="s">
         <v>483</v>
       </c>
-      <c r="J10" t="s">
+      <c r="M10" t="s">
         <v>484</v>
-      </c>
-      <c r="K10" t="s">
-        <v>485</v>
-      </c>
-      <c r="L10" t="s">
-        <v>486</v>
-      </c>
-      <c r="M10" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D11" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -9035,36 +9016,36 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
+        <v>486</v>
+      </c>
+      <c r="I11" t="s">
+        <v>487</v>
+      </c>
+      <c r="J11" t="s">
+        <v>488</v>
+      </c>
+      <c r="K11" t="s">
         <v>489</v>
       </c>
-      <c r="I11" t="s">
+      <c r="L11" t="s">
         <v>490</v>
       </c>
-      <c r="J11" t="s">
+      <c r="M11" t="s">
         <v>491</v>
-      </c>
-      <c r="K11" t="s">
-        <v>492</v>
-      </c>
-      <c r="L11" t="s">
-        <v>493</v>
-      </c>
-      <c r="M11" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D12" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -9076,36 +9057,36 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
+        <v>493</v>
+      </c>
+      <c r="I12" t="s">
+        <v>494</v>
+      </c>
+      <c r="J12" t="s">
+        <v>495</v>
+      </c>
+      <c r="K12" t="s">
         <v>496</v>
       </c>
-      <c r="I12" t="s">
+      <c r="L12" t="s">
         <v>497</v>
       </c>
-      <c r="J12" t="s">
+      <c r="M12" t="s">
         <v>498</v>
-      </c>
-      <c r="K12" t="s">
-        <v>499</v>
-      </c>
-      <c r="L12" t="s">
-        <v>500</v>
-      </c>
-      <c r="M12" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D13" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -9117,36 +9098,36 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
+        <v>500</v>
+      </c>
+      <c r="I13" t="s">
+        <v>501</v>
+      </c>
+      <c r="J13" t="s">
+        <v>502</v>
+      </c>
+      <c r="K13" t="s">
         <v>503</v>
       </c>
-      <c r="I13" t="s">
+      <c r="L13" t="s">
         <v>504</v>
       </c>
-      <c r="J13" t="s">
+      <c r="M13" t="s">
         <v>505</v>
-      </c>
-      <c r="K13" t="s">
-        <v>506</v>
-      </c>
-      <c r="L13" t="s">
-        <v>507</v>
-      </c>
-      <c r="M13" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D14" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -9158,36 +9139,36 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
+        <v>507</v>
+      </c>
+      <c r="I14" t="s">
+        <v>508</v>
+      </c>
+      <c r="J14" t="s">
+        <v>509</v>
+      </c>
+      <c r="K14" t="s">
         <v>510</v>
       </c>
-      <c r="I14" t="s">
+      <c r="L14" t="s">
         <v>511</v>
       </c>
-      <c r="J14" t="s">
+      <c r="M14" t="s">
         <v>512</v>
-      </c>
-      <c r="K14" t="s">
-        <v>513</v>
-      </c>
-      <c r="L14" t="s">
-        <v>514</v>
-      </c>
-      <c r="M14" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D15" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -9199,39 +9180,39 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
+        <v>514</v>
+      </c>
+      <c r="I15" t="s">
+        <v>515</v>
+      </c>
+      <c r="J15" t="s">
+        <v>516</v>
+      </c>
+      <c r="K15" t="s">
         <v>517</v>
       </c>
-      <c r="I15" t="s">
+      <c r="L15" t="s">
         <v>518</v>
       </c>
-      <c r="J15" t="s">
+      <c r="M15" t="s">
         <v>519</v>
-      </c>
-      <c r="K15" t="s">
-        <v>520</v>
-      </c>
-      <c r="L15" t="s">
-        <v>521</v>
-      </c>
-      <c r="M15" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D16" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E16" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -9240,39 +9221,39 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
+        <v>523</v>
+      </c>
+      <c r="I16" t="s">
+        <v>524</v>
+      </c>
+      <c r="J16" t="s">
+        <v>525</v>
+      </c>
+      <c r="K16" t="s">
         <v>526</v>
       </c>
-      <c r="I16" t="s">
+      <c r="L16" t="s">
         <v>527</v>
       </c>
-      <c r="J16" t="s">
+      <c r="M16" t="s">
         <v>528</v>
-      </c>
-      <c r="K16" t="s">
-        <v>529</v>
-      </c>
-      <c r="L16" t="s">
-        <v>530</v>
-      </c>
-      <c r="M16" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D17" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E17" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -9281,39 +9262,39 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
+        <v>531</v>
+      </c>
+      <c r="I17" t="s">
+        <v>532</v>
+      </c>
+      <c r="J17" t="s">
+        <v>533</v>
+      </c>
+      <c r="K17" t="s">
         <v>534</v>
       </c>
-      <c r="I17" t="s">
+      <c r="L17" t="s">
         <v>535</v>
       </c>
-      <c r="J17" t="s">
+      <c r="M17" t="s">
         <v>536</v>
-      </c>
-      <c r="K17" t="s">
-        <v>537</v>
-      </c>
-      <c r="L17" t="s">
-        <v>538</v>
-      </c>
-      <c r="M17" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D18" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E18" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -9322,39 +9303,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
+        <v>539</v>
+      </c>
+      <c r="I18" t="s">
+        <v>540</v>
+      </c>
+      <c r="J18" t="s">
+        <v>541</v>
+      </c>
+      <c r="K18" t="s">
         <v>542</v>
       </c>
-      <c r="I18" t="s">
+      <c r="L18" t="s">
         <v>543</v>
       </c>
-      <c r="J18" t="s">
+      <c r="M18" t="s">
         <v>544</v>
-      </c>
-      <c r="K18" t="s">
-        <v>545</v>
-      </c>
-      <c r="L18" t="s">
-        <v>546</v>
-      </c>
-      <c r="M18" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D19" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E19" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -9363,39 +9344,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
+        <v>547</v>
+      </c>
+      <c r="I19" t="s">
+        <v>548</v>
+      </c>
+      <c r="J19" t="s">
+        <v>549</v>
+      </c>
+      <c r="K19" t="s">
         <v>550</v>
       </c>
-      <c r="I19" t="s">
+      <c r="L19" t="s">
         <v>551</v>
       </c>
-      <c r="J19" t="s">
+      <c r="M19" t="s">
         <v>552</v>
-      </c>
-      <c r="K19" t="s">
-        <v>553</v>
-      </c>
-      <c r="L19" t="s">
-        <v>554</v>
-      </c>
-      <c r="M19" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D20" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E20" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -9404,39 +9385,39 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
+        <v>555</v>
+      </c>
+      <c r="I20" t="s">
+        <v>556</v>
+      </c>
+      <c r="J20" t="s">
+        <v>557</v>
+      </c>
+      <c r="K20" t="s">
         <v>558</v>
       </c>
-      <c r="I20" t="s">
+      <c r="L20" t="s">
         <v>559</v>
       </c>
-      <c r="J20" t="s">
+      <c r="M20" t="s">
         <v>560</v>
-      </c>
-      <c r="K20" t="s">
-        <v>561</v>
-      </c>
-      <c r="L20" t="s">
-        <v>562</v>
-      </c>
-      <c r="M20" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D21" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E21" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -9445,39 +9426,39 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
+        <v>563</v>
+      </c>
+      <c r="I21" t="s">
+        <v>564</v>
+      </c>
+      <c r="J21" t="s">
+        <v>565</v>
+      </c>
+      <c r="K21" t="s">
         <v>566</v>
       </c>
-      <c r="I21" t="s">
+      <c r="L21" t="s">
         <v>567</v>
       </c>
-      <c r="J21" t="s">
+      <c r="M21" t="s">
         <v>568</v>
-      </c>
-      <c r="K21" t="s">
-        <v>569</v>
-      </c>
-      <c r="L21" t="s">
-        <v>570</v>
-      </c>
-      <c r="M21" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D22" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E22" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -9486,39 +9467,39 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
+        <v>571</v>
+      </c>
+      <c r="I22" t="s">
+        <v>572</v>
+      </c>
+      <c r="J22" t="s">
+        <v>573</v>
+      </c>
+      <c r="K22" t="s">
         <v>574</v>
       </c>
-      <c r="I22" t="s">
+      <c r="L22" t="s">
         <v>575</v>
       </c>
-      <c r="J22" t="s">
+      <c r="M22" t="s">
         <v>576</v>
-      </c>
-      <c r="K22" t="s">
-        <v>577</v>
-      </c>
-      <c r="L22" t="s">
-        <v>578</v>
-      </c>
-      <c r="M22" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D23" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E23" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -9527,39 +9508,39 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
+        <v>580</v>
+      </c>
+      <c r="I23" t="s">
+        <v>581</v>
+      </c>
+      <c r="J23" t="s">
+        <v>582</v>
+      </c>
+      <c r="K23" t="s">
         <v>583</v>
       </c>
-      <c r="I23" t="s">
+      <c r="L23" t="s">
         <v>584</v>
       </c>
-      <c r="J23" t="s">
+      <c r="M23" t="s">
         <v>585</v>
-      </c>
-      <c r="K23" t="s">
-        <v>586</v>
-      </c>
-      <c r="L23" t="s">
-        <v>587</v>
-      </c>
-      <c r="M23" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D24" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E24" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -9568,39 +9549,39 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
+        <v>588</v>
+      </c>
+      <c r="I24" t="s">
+        <v>589</v>
+      </c>
+      <c r="J24" t="s">
+        <v>590</v>
+      </c>
+      <c r="K24" t="s">
         <v>591</v>
       </c>
-      <c r="I24" t="s">
+      <c r="L24" t="s">
         <v>592</v>
       </c>
-      <c r="J24" t="s">
+      <c r="M24" t="s">
         <v>593</v>
-      </c>
-      <c r="K24" t="s">
-        <v>594</v>
-      </c>
-      <c r="L24" t="s">
-        <v>595</v>
-      </c>
-      <c r="M24" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D25" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E25" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -9609,22 +9590,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="I25" t="s">
         <v>52</v>
       </c>
       <c r="J25" t="s">
+        <v>597</v>
+      </c>
+      <c r="K25" t="s">
+        <v>598</v>
+      </c>
+      <c r="L25" t="s">
+        <v>599</v>
+      </c>
+      <c r="M25" t="s">
         <v>600</v>
-      </c>
-      <c r="K25" t="s">
-        <v>601</v>
-      </c>
-      <c r="L25" t="s">
-        <v>602</v>
-      </c>
-      <c r="M25" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -9632,10 +9613,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D26" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -9647,22 +9628,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
+        <v>603</v>
+      </c>
+      <c r="I26" t="s">
+        <v>604</v>
+      </c>
+      <c r="J26" t="s">
+        <v>605</v>
+      </c>
+      <c r="K26" t="s">
         <v>606</v>
       </c>
-      <c r="I26" t="s">
+      <c r="L26" t="s">
         <v>607</v>
       </c>
-      <c r="J26" t="s">
+      <c r="M26" t="s">
         <v>608</v>
-      </c>
-      <c r="K26" t="s">
-        <v>609</v>
-      </c>
-      <c r="L26" t="s">
-        <v>610</v>
-      </c>
-      <c r="M26" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -9670,13 +9651,13 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D27" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E27" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -9685,36 +9666,36 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
+        <v>611</v>
+      </c>
+      <c r="I27" t="s">
+        <v>612</v>
+      </c>
+      <c r="J27" t="s">
+        <v>613</v>
+      </c>
+      <c r="K27" t="s">
         <v>614</v>
       </c>
-      <c r="I27" t="s">
+      <c r="L27" t="s">
         <v>615</v>
       </c>
-      <c r="J27" t="s">
+      <c r="M27" t="s">
         <v>616</v>
-      </c>
-      <c r="K27" t="s">
-        <v>617</v>
-      </c>
-      <c r="L27" t="s">
-        <v>618</v>
-      </c>
-      <c r="M27" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="D28" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -9726,36 +9707,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
+        <v>618</v>
+      </c>
+      <c r="I28" t="s">
+        <v>619</v>
+      </c>
+      <c r="J28" t="s">
+        <v>620</v>
+      </c>
+      <c r="K28" t="s">
         <v>621</v>
       </c>
-      <c r="I28" t="s">
+      <c r="L28" t="s">
         <v>622</v>
       </c>
-      <c r="J28" t="s">
+      <c r="M28" t="s">
         <v>623</v>
-      </c>
-      <c r="K28" t="s">
-        <v>624</v>
-      </c>
-      <c r="L28" t="s">
-        <v>625</v>
-      </c>
-      <c r="M28" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D29" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -9767,36 +9748,36 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
+        <v>625</v>
+      </c>
+      <c r="I29" t="s">
+        <v>626</v>
+      </c>
+      <c r="J29" t="s">
+        <v>627</v>
+      </c>
+      <c r="K29" t="s">
         <v>628</v>
       </c>
-      <c r="I29" t="s">
+      <c r="L29" t="s">
         <v>629</v>
       </c>
-      <c r="J29" t="s">
+      <c r="M29" t="s">
         <v>630</v>
-      </c>
-      <c r="K29" t="s">
-        <v>631</v>
-      </c>
-      <c r="L29" t="s">
-        <v>632</v>
-      </c>
-      <c r="M29" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D30" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E30" t="s">
         <v>2</v>
@@ -9808,39 +9789,39 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
+        <v>632</v>
+      </c>
+      <c r="I30" t="s">
+        <v>633</v>
+      </c>
+      <c r="J30" t="s">
+        <v>634</v>
+      </c>
+      <c r="K30" t="s">
         <v>635</v>
       </c>
-      <c r="I30" t="s">
+      <c r="L30" t="s">
         <v>636</v>
       </c>
-      <c r="J30" t="s">
+      <c r="M30" t="s">
         <v>637</v>
-      </c>
-      <c r="K30" t="s">
-        <v>638</v>
-      </c>
-      <c r="L30" t="s">
-        <v>639</v>
-      </c>
-      <c r="M30" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D31" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E31" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -9849,22 +9830,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
+        <v>639</v>
+      </c>
+      <c r="I31" t="s">
+        <v>640</v>
+      </c>
+      <c r="J31" t="s">
+        <v>641</v>
+      </c>
+      <c r="K31" t="s">
         <v>642</v>
       </c>
-      <c r="I31" t="s">
+      <c r="L31" t="s">
         <v>643</v>
       </c>
-      <c r="J31" t="s">
+      <c r="M31" t="s">
         <v>644</v>
-      </c>
-      <c r="K31" t="s">
-        <v>645</v>
-      </c>
-      <c r="L31" t="s">
-        <v>646</v>
-      </c>
-      <c r="M31" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -9872,13 +9853,13 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D32" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E32" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -9887,22 +9868,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
+        <v>647</v>
+      </c>
+      <c r="I32" t="s">
+        <v>648</v>
+      </c>
+      <c r="J32" t="s">
+        <v>649</v>
+      </c>
+      <c r="K32" t="s">
         <v>650</v>
       </c>
-      <c r="I32" t="s">
+      <c r="L32" t="s">
         <v>651</v>
       </c>
-      <c r="J32" t="s">
+      <c r="M32" t="s">
         <v>652</v>
-      </c>
-      <c r="K32" t="s">
-        <v>653</v>
-      </c>
-      <c r="L32" t="s">
-        <v>654</v>
-      </c>
-      <c r="M32" t="s">
-        <v>655</v>
       </c>
     </row>
   </sheetData>
